--- a/ExcelTable/Unit.xlsx
+++ b/ExcelTable/Unit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DevD\CommonModule\ExcelTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B4F03F0-6142-4394-AE2B-6B083B0E587D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9C6CFB8-FFE0-46CB-82FB-D58485214E5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5040" yWindow="1245" windowWidth="19515" windowHeight="12465" tabRatio="894" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -68,9 +68,6 @@
     <t>근거리</t>
   </si>
   <si>
-    <t>슬라임</t>
-  </si>
-  <si>
     <t>Monster/01_slime</t>
   </si>
   <si>
@@ -117,6 +114,10 @@
   </si>
   <si>
     <t>Monster/9999_Dummy</t>
+  </si>
+  <si>
+    <t>히어로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -194,7 +195,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -219,6 +220,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -642,19 +646,19 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" ht="16.5">
       <c r="A4">
         <v>1001</v>
       </c>
       <c r="B4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>11</v>
+      <c r="C4" s="10" t="s">
+        <v>27</v>
       </c>
       <c r="D4" s="8"/>
       <c r="E4" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F4" s="3">
         <v>200</v>
@@ -671,11 +675,11 @@
         <v>10</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F5" s="3">
         <v>200</v>
@@ -689,14 +693,14 @@
         <v>1003</v>
       </c>
       <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F6" s="3">
         <v>200</v>
@@ -713,11 +717,11 @@
         <v>10</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D7" s="8"/>
       <c r="E7" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F7" s="3">
         <v>300</v>
@@ -731,14 +735,14 @@
         <v>1005</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F8" s="3">
         <v>200</v>
@@ -752,13 +756,13 @@
         <v>1006</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" t="s">
         <v>22</v>
-      </c>
-      <c r="E9" t="s">
-        <v>23</v>
       </c>
       <c r="F9">
         <v>200</v>
@@ -772,13 +776,13 @@
         <v>2001</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" t="s">
         <v>24</v>
-      </c>
-      <c r="E10" t="s">
-        <v>25</v>
       </c>
       <c r="F10">
         <v>5000</v>
@@ -792,13 +796,13 @@
         <v>2002</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" t="s">
         <v>24</v>
-      </c>
-      <c r="E11" t="s">
-        <v>25</v>
       </c>
       <c r="F11">
         <v>5000</v>
@@ -812,13 +816,13 @@
         <v>9001</v>
       </c>
       <c r="B12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" t="s">
         <v>26</v>
-      </c>
-      <c r="C12" t="s">
-        <v>26</v>
-      </c>
-      <c r="E12" t="s">
-        <v>27</v>
       </c>
       <c r="F12">
         <v>1000000</v>

--- a/ExcelTable/Unit.xlsx
+++ b/ExcelTable/Unit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DevD\CommonModule\ExcelTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9C6CFB8-FFE0-46CB-82FB-D58485214E5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1417D118-5FEE-4C78-A564-58DA7BE103E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5040" yWindow="1245" windowWidth="19515" windowHeight="12465" tabRatio="894" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1860" yWindow="1815" windowWidth="22920" windowHeight="12465" tabRatio="894" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Unit" sheetId="18" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="21">
   <si>
     <t>int</t>
   </si>
@@ -56,67 +56,48 @@
     <t>Icon</t>
   </si>
   <si>
+    <t>Hp</t>
+  </si>
+  <si>
+    <t>Damage</t>
+  </si>
+  <si>
+    <t>근거리</t>
+  </si>
+  <si>
+    <t>스켈레톤 소드</t>
+  </si>
+  <si>
+    <t>원거리</t>
+  </si>
+  <si>
+    <t>스켈레톤 메이지</t>
+  </si>
+  <si>
+    <t>스켈레톤 워리어</t>
+  </si>
+  <si>
+    <t>눈발사람</t>
+  </si>
+  <si>
+    <t>스켈보틀</t>
+  </si>
+  <si>
+    <t>스켈레톤 보스</t>
+  </si>
+  <si>
+    <t>허수아비</t>
+  </si>
+  <si>
+    <t>히어로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>PrefabName</t>
-  </si>
-  <si>
-    <t>Hp</t>
-  </si>
-  <si>
-    <t>Damage</t>
-  </si>
-  <si>
-    <t>근거리</t>
-  </si>
-  <si>
-    <t>Monster/01_slime</t>
-  </si>
-  <si>
-    <t>스켈레톤 소드</t>
-  </si>
-  <si>
-    <t>Monster/skeleton_sword</t>
-  </si>
-  <si>
-    <t>원거리</t>
-  </si>
-  <si>
-    <t>스켈레톤 메이지</t>
-  </si>
-  <si>
-    <t>Monster/skeleton_mage</t>
-  </si>
-  <si>
-    <t>스켈레톤 워리어</t>
-  </si>
-  <si>
-    <t>Monster/skeleton_warrior</t>
-  </si>
-  <si>
-    <t>눈발사람</t>
-  </si>
-  <si>
-    <t>Monster/5_snow_bomb</t>
-  </si>
-  <si>
-    <t>스켈보틀</t>
-  </si>
-  <si>
-    <t>Monster/6_poison_bomb</t>
-  </si>
-  <si>
-    <t>스켈레톤 보스</t>
-  </si>
-  <si>
-    <t>Monster/skeleton_boss</t>
-  </si>
-  <si>
-    <t>허수아비</t>
-  </si>
-  <si>
-    <t>Monster/9999_Dummy</t>
-  </si>
-  <si>
-    <t>히어로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Monster/ZombieObj</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -590,14 +571,14 @@
       <c r="D1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="G1" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -651,14 +632,14 @@
         <v>1001</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D4" s="8"/>
       <c r="E4" s="8" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F4" s="3">
         <v>200</v>
@@ -672,14 +653,14 @@
         <v>1002</v>
       </c>
       <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>12</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F5" s="3">
         <v>200</v>
@@ -693,14 +674,14 @@
         <v>1003</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F6" s="3">
         <v>200</v>
@@ -714,14 +695,14 @@
         <v>1004</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D7" s="8"/>
       <c r="E7" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F7" s="3">
         <v>300</v>
@@ -735,10 +716,10 @@
         <v>1005</v>
       </c>
       <c r="B8" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>14</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>19</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="8" t="s">
@@ -756,13 +737,13 @@
         <v>1006</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" t="s">
-        <v>22</v>
+        <v>15</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>20</v>
       </c>
       <c r="F9">
         <v>200</v>
@@ -776,13 +757,13 @@
         <v>2001</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10" t="s">
-        <v>24</v>
+        <v>16</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>20</v>
       </c>
       <c r="F10">
         <v>5000</v>
@@ -796,13 +777,13 @@
         <v>2002</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" t="s">
-        <v>24</v>
+        <v>16</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>20</v>
       </c>
       <c r="F11">
         <v>5000</v>
@@ -816,13 +797,13 @@
         <v>9001</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" t="s">
-        <v>26</v>
+        <v>17</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>20</v>
       </c>
       <c r="F12">
         <v>1000000</v>
